--- a/artfynd/A 22873-2026 artfynd.xlsx
+++ b/artfynd/A 22873-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>105034634</v>
       </c>
       <c r="B2" t="n">
-        <v>57577</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -728,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571883.5534008238</v>
+        <v>571884</v>
       </c>
       <c r="R2" t="n">
-        <v>7267847.080949021</v>
+        <v>7267847</v>
       </c>
       <c r="S2" t="n">
         <v>75</v>
@@ -761,19 +756,9 @@
           <t>2022-05-31</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-05-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,127 +785,6 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Internationell Herptilinventering med Svensk bas</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>107165930</v>
-      </c>
-      <c r="B3" t="n">
-        <v>57435</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>100077</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Utter</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Lutra lutra</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Vackertjärnen (AC2399), Ly lm</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>571914.9173098039</v>
-      </c>
-      <c r="R3" t="n">
-        <v>7267637.049926553</v>
-      </c>
-      <c r="S3" t="n">
-        <v>100</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Stensele</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>AC2399</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2018-09-17</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2018-09-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Darius Strasevicius</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Via Darius Strasevicius</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Utter barmarksinventering RMÖ/GDP</t>
         </is>
       </c>
     </row>
